--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1800,6 +1815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2537,6 +2557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3422,6 +3447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4159,6 +4189,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4896,6 +4931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5781,6 +5821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6518,6 +6563,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7403,6 +7453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8140,6 +8195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8877,6 +8937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9762,6 +9827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10499,6 +10569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11236,6 +11311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11973,6 +12053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12858,6 +12943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13595,6 +13685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14480,6 +14575,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15217,6 +15317,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15954,6 +16059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16839,6 +16949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17574,6 +17689,11 @@
       <c r="S116" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">

--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -1226,28 +1226,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1374,28 +1388,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1522,28 +1550,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1670,28 +1712,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1968,28 +2024,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2116,28 +2186,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2264,28 +2348,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2412,28 +2510,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2710,28 +2822,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2858,28 +2984,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3006,28 +3146,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3154,28 +3308,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3302,28 +3470,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -3600,28 +3782,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3748,28 +3944,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -3896,28 +4106,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4044,28 +4268,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4342,28 +4580,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4490,28 +4742,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -4638,28 +4904,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4786,28 +5066,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5084,28 +5378,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5232,28 +5540,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5380,28 +5702,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -5528,28 +5864,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5676,28 +6026,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5974,28 +6338,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6122,28 +6500,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -6270,28 +6662,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6418,28 +6824,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6716,28 +7136,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -6864,28 +7298,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7012,28 +7460,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -7160,28 +7622,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7308,28 +7784,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7606,28 +8096,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -7754,28 +8258,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -7902,28 +8420,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8050,28 +8582,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8348,28 +8894,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8496,28 +9056,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8644,28 +9218,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8792,28 +9380,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -9090,28 +9692,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9238,28 +9854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -9386,28 +10016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9534,28 +10178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9682,28 +10340,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9980,28 +10652,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10128,28 +10814,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -10276,28 +10976,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10424,28 +11138,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10722,28 +11450,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -10870,28 +11612,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -11018,28 +11774,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11166,28 +11936,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11464,28 +12248,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11612,28 +12410,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -11760,28 +12572,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -11908,28 +12734,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12206,28 +13046,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12354,28 +13208,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12502,28 +13370,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -12650,28 +13532,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12798,28 +13694,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -13096,28 +14006,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13244,28 +14168,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -13392,28 +14330,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13540,28 +14492,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13838,28 +14804,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -13986,28 +14966,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -14134,28 +15128,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -14282,28 +15290,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14430,28 +15452,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14728,28 +15764,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -14876,28 +15926,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -15024,28 +16088,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15172,28 +16250,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15470,28 +16562,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15618,28 +16724,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -15766,28 +16886,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -15914,28 +17048,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -16212,28 +17360,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -16360,28 +17522,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16508,28 +17684,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -16656,28 +17846,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -16804,28 +18008,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17102,28 +18320,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -17250,28 +18482,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -17398,28 +18644,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17546,28 +18806,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -17844,28 +19118,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -17992,28 +19280,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18140,28 +19442,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -18288,28 +19604,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">

--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1866,11 +1821,6 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1883,22 +1833,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2664,11 +2604,6 @@
       <c r="R14" t="n">
         <v>0.013980102260254</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2681,22 +2616,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3624,11 +3549,6 @@
       <c r="R20" t="n">
         <v>0.007988629863002287</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3641,22 +3561,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4422,11 +4332,6 @@
       <c r="R25" t="n">
         <v>0.01997157465750572</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4439,22 +4344,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -5220,11 +5115,6 @@
       <c r="R30" t="n">
         <v>0.01198294479450343</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5237,22 +5127,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -6180,11 +6060,6 @@
       <c r="R36" t="n">
         <v>0.003994314931501143</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6197,22 +6072,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6978,11 +6843,6 @@
       <c r="R41" t="n">
         <v>0.009985787328752859</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6995,22 +6855,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7938,11 +7788,6 @@
       <c r="R47" t="n">
         <v>0.003994314931501143</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7955,22 +7800,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8736,11 +8571,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8753,22 +8583,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -9534,11 +9354,6 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9551,22 +9366,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -10494,11 +10299,6 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10511,22 +10311,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -11292,11 +11082,6 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11309,22 +11094,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -12090,11 +11865,6 @@
       <c r="R73" t="n">
         <v>0.001978667765170246</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12107,22 +11877,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -12888,11 +12648,6 @@
       <c r="R78" t="n">
         <v>0.003957335530340491</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12905,22 +12660,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -13848,11 +13593,6 @@
       <c r="R84" t="n">
         <v>0.01385067435619172</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13865,22 +13605,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -14646,11 +14376,6 @@
       <c r="R89" t="n">
         <v>0.0217653454168727</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14663,22 +14388,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -15606,11 +15321,6 @@
       <c r="R95" t="n">
         <v>0.01780800988653221</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15623,22 +15333,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -16404,11 +16104,6 @@
       <c r="R100" t="n">
         <v>0.0217653454168727</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16421,22 +16116,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -17202,11 +16887,6 @@
       <c r="R105" t="n">
         <v>0.02374401318204294</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17219,22 +16899,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -18162,11 +17832,6 @@
       <c r="R111" t="n">
         <v>0.003957335530340491</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18179,22 +17844,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -18960,11 +18615,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18977,22 +18627,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>

--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -1170,17 +1170,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -1188,7 +1186,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1198,12 +1196,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1213,11 +1206,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1332,17 +1320,15 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -1350,7 +1336,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1360,12 +1346,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1375,11 +1356,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1494,17 +1470,15 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -1512,7 +1486,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1522,12 +1496,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1537,11 +1506,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1656,17 +1620,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -1674,7 +1636,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1684,12 +1646,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1699,11 +1656,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1953,17 +1905,15 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -1971,7 +1921,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1981,12 +1931,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1996,11 +1941,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2115,17 +2055,15 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -2133,7 +2071,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2143,12 +2081,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2158,11 +2091,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2277,17 +2205,15 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -2295,7 +2221,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2305,12 +2231,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2320,11 +2241,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2439,17 +2355,15 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -2457,7 +2371,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2467,12 +2381,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2482,11 +2391,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2736,17 +2640,15 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -2754,7 +2656,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2764,12 +2666,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2779,11 +2676,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2898,17 +2790,15 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -2916,7 +2806,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2926,12 +2816,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -2941,11 +2826,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3060,17 +2940,15 @@
       <c r="O17" t="n">
         <v>2</v>
       </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -3078,7 +2956,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3088,12 +2966,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3103,11 +2976,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3222,17 +3090,15 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -3240,7 +3106,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3250,12 +3116,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3265,11 +3126,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3384,17 +3240,15 @@
       <c r="O19" t="n">
         <v>3</v>
       </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -3402,7 +3256,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3412,12 +3266,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3427,11 +3276,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3681,17 +3525,15 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -3699,7 +3541,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3709,12 +3551,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3724,11 +3561,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3843,17 +3675,15 @@
       <c r="O22" t="n">
         <v>3</v>
       </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -3861,7 +3691,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3871,12 +3701,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -3886,11 +3711,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4005,17 +3825,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4023,7 +3841,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4033,12 +3851,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4048,11 +3861,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4167,17 +3975,15 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4185,7 +3991,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4195,12 +4001,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4210,11 +4011,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4464,17 +4260,15 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4482,7 +4276,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4492,12 +4286,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4507,11 +4296,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4626,17 +4410,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4644,7 +4426,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4654,12 +4436,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4669,11 +4446,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4788,17 +4560,15 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4806,7 +4576,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4816,12 +4586,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4831,11 +4596,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4950,17 +4710,15 @@
       <c r="O29" t="n">
         <v>3</v>
       </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -4968,7 +4726,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4978,12 +4736,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -4993,11 +4746,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5247,17 +4995,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -5265,7 +5011,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5275,12 +5021,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5290,11 +5031,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5409,17 +5145,15 @@
       <c r="O32" t="n">
         <v>5</v>
       </c>
+      <c r="P32" t="n">
+        <v>5</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -5427,7 +5161,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5437,12 +5171,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5452,11 +5181,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5571,17 +5295,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -5589,7 +5311,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5599,12 +5321,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -5614,11 +5331,6 @@
       </c>
       <c r="AT33" t="n">
         <v>1</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5733,17 +5445,15 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -5751,7 +5461,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5761,12 +5471,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5776,11 +5481,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5895,17 +5595,15 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -5913,7 +5611,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5923,12 +5621,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -5938,11 +5631,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6192,17 +5880,15 @@
       <c r="O37" t="n">
         <v>2</v>
       </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -6210,7 +5896,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6220,12 +5906,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6235,11 +5916,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6354,17 +6030,15 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -6372,7 +6046,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6382,12 +6056,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -6397,11 +6066,6 @@
       </c>
       <c r="AT38" t="n">
         <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6516,17 +6180,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -6534,7 +6196,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6544,12 +6206,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6559,11 +6216,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6678,17 +6330,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -6696,7 +6346,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6706,12 +6356,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6721,11 +6366,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6975,17 +6615,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -6993,7 +6631,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7003,12 +6641,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7018,11 +6651,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7137,17 +6765,15 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -7155,7 +6781,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7165,12 +6791,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7180,11 +6801,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7299,17 +6915,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -7317,7 +6931,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7327,12 +6941,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -7342,11 +6951,6 @@
       </c>
       <c r="AT44" t="n">
         <v>1</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7461,17 +7065,15 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -7479,7 +7081,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7489,12 +7091,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7504,11 +7101,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7623,17 +7215,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -7641,7 +7231,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7651,12 +7241,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7666,11 +7251,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7920,17 +7500,15 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -7938,7 +7516,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7948,12 +7526,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -7963,11 +7536,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8082,17 +7650,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -8100,7 +7666,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8110,12 +7676,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -8125,11 +7686,6 @@
       </c>
       <c r="AT49" t="n">
         <v>1</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8244,17 +7800,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -8262,7 +7816,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8272,12 +7826,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8287,11 +7836,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8406,17 +7950,15 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -8424,7 +7966,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8434,12 +7976,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8449,11 +7986,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8703,17 +8235,15 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -8721,7 +8251,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8731,12 +8261,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8746,11 +8271,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8865,17 +8385,15 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -8883,7 +8401,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8893,12 +8411,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -8908,11 +8421,6 @@
       </c>
       <c r="AT54" t="n">
         <v>1</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9027,17 +8535,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9045,7 +8551,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9055,12 +8561,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9070,11 +8571,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9189,17 +8685,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9207,7 +8701,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9217,12 +8711,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9232,11 +8721,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9486,17 +8970,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9504,7 +8986,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9514,12 +8996,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -9529,11 +9006,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9648,17 +9120,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9666,7 +9136,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9676,12 +9146,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
@@ -9691,11 +9156,6 @@
       </c>
       <c r="AT59" t="n">
         <v>1</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9810,17 +9270,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9828,7 +9286,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9838,12 +9296,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -9853,11 +9306,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9972,17 +9420,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -9990,7 +9436,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10000,12 +9446,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10015,11 +9456,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10134,17 +9570,15 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -10152,7 +9586,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10162,12 +9596,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -10177,11 +9606,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10431,17 +9855,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -10449,7 +9871,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10459,12 +9881,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -10474,11 +9891,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10593,17 +10005,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -10611,7 +10021,7 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10621,12 +10031,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
@@ -10636,11 +10041,6 @@
       </c>
       <c r="AT65" t="n">
         <v>1</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10755,17 +10155,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -10773,7 +10171,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10783,12 +10181,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10798,11 +10191,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10917,17 +10305,15 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -10935,7 +10321,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10945,12 +10331,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -10960,11 +10341,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11214,17 +10590,15 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -11232,7 +10606,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11242,12 +10616,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -11257,11 +10626,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11376,17 +10740,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -11394,7 +10756,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11404,12 +10766,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ70" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
@@ -11419,11 +10776,6 @@
       </c>
       <c r="AT70" t="n">
         <v>1</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11538,17 +10890,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -11556,7 +10906,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11566,12 +10916,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11581,11 +10926,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11700,17 +11040,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -11718,7 +11056,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11728,12 +11066,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11743,11 +11076,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11997,17 +11325,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12015,7 +11341,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12025,12 +11351,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -12040,11 +11361,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12159,17 +11475,15 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U75" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12177,7 +11491,7 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12187,12 +11501,7 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
@@ -12202,11 +11511,6 @@
       </c>
       <c r="AT75" t="n">
         <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12321,17 +11625,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12339,7 +11641,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12349,12 +11651,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -12364,11 +11661,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12483,17 +11775,15 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12501,7 +11791,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12511,12 +11801,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12526,11 +11811,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12780,17 +12060,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12798,7 +12076,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12808,12 +12086,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -12823,11 +12096,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12942,17 +12210,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -12960,7 +12226,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12970,12 +12236,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -12985,11 +12246,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13104,17 +12360,15 @@
       <c r="O81" t="n">
         <v>2</v>
       </c>
+      <c r="P81" t="n">
+        <v>2</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U81" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -13122,7 +12376,7 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13132,12 +12386,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
@@ -13147,11 +12396,6 @@
       </c>
       <c r="AT81" t="n">
         <v>1</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13266,17 +12510,15 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
+      <c r="P82" t="n">
+        <v>2</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -13284,7 +12526,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13294,12 +12536,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -13309,11 +12546,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13428,17 +12660,15 @@
       <c r="O83" t="n">
         <v>2</v>
       </c>
+      <c r="P83" t="n">
+        <v>2</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -13446,7 +12676,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13456,12 +12686,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13471,11 +12696,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13725,17 +12945,15 @@
       <c r="O85" t="n">
         <v>2</v>
       </c>
+      <c r="P85" t="n">
+        <v>2</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -13743,7 +12961,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13753,12 +12971,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -13768,11 +12981,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13887,17 +13095,15 @@
       <c r="O86" t="n">
         <v>2</v>
       </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -13905,7 +13111,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -13915,12 +13121,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
@@ -13930,11 +13131,6 @@
       </c>
       <c r="AT86" t="n">
         <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14049,17 +13245,15 @@
       <c r="O87" t="n">
         <v>4</v>
       </c>
+      <c r="P87" t="n">
+        <v>4</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -14067,7 +13261,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14077,12 +13271,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -14092,11 +13281,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14211,17 +13395,15 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
+      <c r="P88" t="n">
+        <v>2</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -14229,7 +13411,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14239,12 +13421,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -14254,11 +13431,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14508,17 +13680,15 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
+      <c r="P90" t="n">
+        <v>1</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -14526,7 +13696,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14536,12 +13706,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -14551,11 +13716,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14670,17 +13830,15 @@
       <c r="O91" t="n">
         <v>5</v>
       </c>
+      <c r="P91" t="n">
+        <v>5</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -14688,7 +13846,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14698,12 +13856,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -14713,11 +13866,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14832,17 +13980,15 @@
       <c r="O92" t="n">
         <v>2</v>
       </c>
+      <c r="P92" t="n">
+        <v>2</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U92" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -14850,7 +13996,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14860,12 +14006,7 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
@@ -14875,11 +14016,6 @@
       </c>
       <c r="AT92" t="n">
         <v>1</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14994,17 +14130,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15012,7 +14146,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15022,12 +14156,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -15037,11 +14166,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -15156,17 +14280,15 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15174,7 +14296,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15184,12 +14306,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -15199,11 +14316,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15453,17 +14565,15 @@
       <c r="O96" t="n">
         <v>4</v>
       </c>
+      <c r="P96" t="n">
+        <v>4</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15471,7 +14581,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15481,12 +14591,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -15496,11 +14601,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15615,17 +14715,15 @@
       <c r="O97" t="n">
         <v>2</v>
       </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15633,7 +14731,7 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15643,12 +14741,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -15658,11 +14751,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15777,17 +14865,15 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
+      <c r="P98" t="n">
+        <v>2</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15795,7 +14881,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -15805,12 +14891,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -15820,11 +14901,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15939,17 +15015,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -15957,7 +15031,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -15967,12 +15041,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15982,11 +15051,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -16236,17 +15300,15 @@
       <c r="O101" t="n">
         <v>8</v>
       </c>
+      <c r="P101" t="n">
+        <v>8</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -16254,7 +15316,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16264,12 +15326,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -16279,11 +15336,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16398,17 +15450,15 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
+      <c r="P102" t="n">
+        <v>2</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -16416,7 +15466,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16426,12 +15476,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -16441,11 +15486,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16560,17 +15600,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -16578,7 +15616,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16588,12 +15626,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -16603,11 +15636,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16722,17 +15750,15 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -16740,7 +15766,7 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -16750,12 +15776,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16765,11 +15786,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -17019,17 +16035,15 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17037,7 +16051,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -17047,12 +16061,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -17062,11 +16071,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -17181,17 +16185,15 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17199,7 +16201,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -17209,12 +16211,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -17224,11 +16221,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -17343,17 +16335,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17361,7 +16351,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17371,12 +16361,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -17386,11 +16371,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17505,17 +16485,15 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17523,7 +16501,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -17533,12 +16511,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -17548,11 +16521,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17667,17 +16635,15 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17685,7 +16651,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -17695,12 +16661,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -17710,11 +16671,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17964,17 +16920,15 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -17982,7 +16936,7 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -17992,12 +16946,7 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
@@ -18007,11 +16956,6 @@
       </c>
       <c r="AT112" t="n">
         <v>1</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -18126,17 +17070,15 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -18144,7 +17086,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -18154,12 +17096,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -18169,11 +17106,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18288,17 +17220,15 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -18306,7 +17236,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18316,12 +17246,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -18331,11 +17256,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -18450,17 +17370,15 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -18468,7 +17386,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18478,12 +17396,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -18493,11 +17406,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18747,17 +17655,15 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -18765,7 +17671,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -18775,12 +17681,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -18790,11 +17691,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18909,17 +17805,15 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="n">
+        <v>1</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -18927,7 +17821,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18937,12 +17831,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -18952,11 +17841,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -19071,17 +17955,15 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -19089,7 +17971,7 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19099,12 +17981,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
@@ -19114,11 +17991,6 @@
       </c>
       <c r="AT119" t="n">
         <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -19233,17 +18105,15 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>HOLD_JP_fee824aee7fd5b0869c839f051e6</t>
@@ -19251,7 +18121,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -19261,12 +18131,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
@@ -19276,11 +18141,6 @@
       </c>
       <c r="AT120" t="n">
         <v>1</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>

--- a/diseases/d057/2010-2014.xlsx
+++ b/diseases/d057/2010-2014.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1773,6 +1818,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1785,12 +1835,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2508,6 +2568,11 @@
       <c r="R14" t="n">
         <v>0.013980102260254</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2520,12 +2585,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3393,6 +3468,11 @@
       <c r="R20" t="n">
         <v>0.007988629863002287</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3485,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -4128,6 +4218,11 @@
       <c r="R25" t="n">
         <v>0.01997157465750572</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4140,12 +4235,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4863,6 +4968,11 @@
       <c r="R30" t="n">
         <v>0.01198294479450343</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4875,12 +4985,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5748,6 +5868,11 @@
       <c r="R36" t="n">
         <v>0.003994314931501143</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5760,12 +5885,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6483,6 +6618,11 @@
       <c r="R41" t="n">
         <v>0.009985787328752859</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6495,12 +6635,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7368,6 +7518,11 @@
       <c r="R47" t="n">
         <v>0.003994314931501143</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7380,12 +7535,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8103,6 +8268,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8115,12 +8285,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8838,6 +9018,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8850,12 +9035,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9723,6 +9918,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9735,12 +9935,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10458,6 +10668,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10470,12 +10685,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11193,6 +11418,11 @@
       <c r="R73" t="n">
         <v>0.001978667765170246</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11205,12 +11435,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11928,6 +12168,11 @@
       <c r="R78" t="n">
         <v>0.003957335530340491</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11940,12 +12185,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12813,6 +13068,11 @@
       <c r="R84" t="n">
         <v>0.01385067435619172</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12825,12 +13085,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13548,6 +13818,11 @@
       <c r="R89" t="n">
         <v>0.0217653454168727</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13560,12 +13835,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14433,6 +14718,11 @@
       <c r="R95" t="n">
         <v>0.01780800988653221</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14445,12 +14735,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15168,6 +15468,11 @@
       <c r="R100" t="n">
         <v>0.0217653454168727</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15180,12 +15485,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15903,6 +16218,11 @@
       <c r="R105" t="n">
         <v>0.02374401318204294</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15915,12 +16235,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16788,6 +17118,11 @@
       <c r="R111" t="n">
         <v>0.003957335530340491</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16800,12 +17135,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17523,6 +17868,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17535,12 +17885,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
